--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
         <v>2.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -487,57 +487,57 @@
         <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0.015</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>11.5</v>
+        <v>9.765000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>11.25</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>8.030000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9.5</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="7">
@@ -603,7 +603,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9.5</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -637,13 +637,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.5</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -653,116 +653,116 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.5</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>8.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2.5</v>
       </c>
       <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E12" t="n">
         <v>1.5</v>
       </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>6.025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="14">
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
         <v>2.5</v>
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="15">
@@ -803,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>0.025</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>5.525</v>
       </c>
     </row>
     <row r="16">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -837,73 +837,73 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>7.5</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>7.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>7.25</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2.5</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>0.025</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>4.775</v>
       </c>
     </row>
     <row r="20">
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>0.0175</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -937,32 +937,32 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>6.25</v>
+        <v>4.5175</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2.5</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.5</v>
+        <v>0.0125</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>4.5125</v>
       </c>
     </row>
     <row r="22">
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="E22" t="n">
         <v>1.5</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="23">
@@ -1003,7 +1003,7 @@
         <v>1.5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.9375</v>
+        <v>0.019375</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1012,32 +1012,32 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9375</v>
+        <v>4.019375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2.5</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.25</v>
+        <v>0.015</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>5.75</v>
+        <v>4.015</v>
       </c>
     </row>
     <row r="25">
@@ -1053,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1062,23 +1062,23 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2.5</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>0.02</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1087,113 +1087,113 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.5</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0.015</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>5.5</v>
+        <v>3.515</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2.5</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>0.0125</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>3.5125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2.5</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2.5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1203,7 +1203,7 @@
         <v>0.5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.0125</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1212,32 +1212,157 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3.0125</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2.5</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Finanssivalvonta/ Finansinspektionen</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.525</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Bundesanstalt für Finanzdienstleistungsaufsicht</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Norwegian Ministry of Finance</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Haut Conseil de Stabilité Financière</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.515</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Finansinspektionen</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.51</v>
       </c>
     </row>
   </sheetData>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,7 +653,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>6.515000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -853,7 +853,7 @@
         <v>0.75</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="18">
@@ -1043,32 +1043,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2.5</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.52</v>
+        <v>3.525</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1093,76 +1093,76 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3.515</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2.5</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0125</v>
+        <v>0.015</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3.5125</v>
+        <v>3.515</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2.5</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3.5</v>
+        <v>3.5125</v>
       </c>
     </row>
     <row r="30">
@@ -1243,7 +1243,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Finanssivalvonta/ Finansinspektionen</t>
+          <t>Norwegian Ministry of Finance</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1262,106 +1262,6 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.525</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Bundesanstalt für Finanzdienstleistungsaufsicht</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Norwegian Ministry of Finance</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Haut Conseil de Stabilité Financière</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2.515</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Finansinspektionen</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
         <v>2.51</v>
       </c>
     </row>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
   </sheetData>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
         <v>2.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>13.03</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +503,7 @@
         <v>1.25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.015</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -512,13 +512,13 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>9.765000000000001</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -528,32 +528,32 @@
         <v>2.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -562,32 +562,32 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>8.030000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2.5</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>7.52</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -603,7 +603,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>7.52</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -637,13 +637,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7.51</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -653,116 +653,116 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>2.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7.51</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7.26</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2.5</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>0.015</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>6.515000000000001</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2.5</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.025</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6.025</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.5</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.02</v>
-      </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.02</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>2.5</v>
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>6.02</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -803,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.025</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.525</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -837,73 +837,73 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>5.52</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2.5</v>
       </c>
       <c r="C17" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>5.27</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2.5</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>5.02</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2.5</v>
       </c>
       <c r="C19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.025</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>4.775</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0175</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -937,32 +937,32 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4.5175</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2.5</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0125</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>4.5125</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>1.5</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4.02</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1003,7 +1003,7 @@
         <v>1.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.019375</v>
+        <v>1.9375</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1012,73 +1012,73 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4.019375</v>
+        <v>5.9375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2.5</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.015</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>4.015</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2.5</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.025</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.525</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2.5</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>3.52</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="27">
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3.52</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="28">
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.015</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3.515</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1153,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0125</v>
+        <v>1.25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1162,38 +1162,38 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3.5125</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2.5</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1203,7 +1203,7 @@
         <v>0.5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0125</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1212,57 +1212,32 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3.0125</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2.5</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Norwegian Ministry of Finance</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ISO2</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CCoB</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CCyB</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>GSII/O-SII</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SyRB</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sSyRB</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -481,63 +469,63 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11.25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -556,194 +544,194 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2.5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2.5</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2.5</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2.5</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>2.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.5</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.9375</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8.25</v>
+        <v>5.9375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2.5</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -753,47 +741,47 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2.5</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -803,22 +791,22 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -834,91 +822,91 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>7.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>7.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2.5</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -928,82 +916,82 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2.5</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2.5</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.9375</v>
+        <v>1.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1012,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9375</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="24">
@@ -1034,23 +1022,23 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2.5</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -1062,23 +1050,23 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2.5</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1087,23 +1075,23 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1112,49 +1100,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2.5</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2.5</v>
       </c>
       <c r="C29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="D29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
@@ -1162,23 +1150,23 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2.5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1187,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1213,31 +1201,6 @@
       </c>
       <c r="G31" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -713,7 +713,7 @@
         <v>2.5</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="13">

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -531,17 +531,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -581,17 +581,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -731,14 +731,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -750,23 +750,23 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2.5</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -781,17 +781,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2.5</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,41 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ISO2</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CCoB</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>CCyB</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>GSII/O-SII</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>SyRB</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sSyRB</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -469,113 +481,113 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2.5</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -594,226 +606,226 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2.5</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.5</v>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E10" t="n">
         <v>1.5</v>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2.5</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>1.9375</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>5.9375</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2.5</v>
       </c>
       <c r="C12" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2.5</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2.5</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2.5</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -822,91 +834,91 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>5.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2.5</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2.5</v>
       </c>
       <c r="C18" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2.5</v>
       </c>
       <c r="C19" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -916,32 +928,32 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2.5</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -950,57 +962,57 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2.5</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1034,23 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2.5</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -1050,23 +1062,23 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2.5</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1075,23 +1087,23 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1100,20 +1112,20 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2.5</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>1.25</v>
@@ -1125,48 +1137,48 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2.5</v>
       </c>
       <c r="C29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2.5</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1175,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="31">
@@ -1201,6 +1213,31 @@
       </c>
       <c r="G31" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/downloads/capital_overall_buffers.xlsx
+++ b/reports/downloads/capital_overall_buffers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ISO2</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CCoB</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CCyB</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>GSII/O-SII</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SyRB</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sSyRB</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -481,113 +469,113 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11.25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2.5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
@@ -606,226 +594,226 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2.5</v>
       </c>
       <c r="C8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="n">
         <v>2.25</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2.5</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.5</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>8.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2.5</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2.5</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2.5</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2.5</v>
       </c>
       <c r="C16" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -834,91 +822,91 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>7.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2.5</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2.5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>7.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2.5</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -928,33 +916,33 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2.5</v>
       </c>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.5</v>
       </c>
-      <c r="D21" t="n">
-        <v>2.25</v>
-      </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
@@ -962,57 +950,57 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2.5</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="24">
@@ -1034,23 +1022,23 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2.5</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -1062,23 +1050,23 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2.5</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1087,23 +1075,23 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1112,20 +1100,20 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2.5</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="n">
         <v>1.25</v>
@@ -1137,38 +1125,38 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2.5</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="D29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1178,7 +1166,7 @@
         <v>0.5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1187,23 +1175,23 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2.5</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1212,32 +1200,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
   </sheetData>
